--- a/data/trans_dic/P13A_1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_2023-Estudios-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,39; 97,74</t>
+          <t>84,01; 97,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,28; 98,79</t>
+          <t>87,29; 98,69</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,66; 99,79</t>
+          <t>90,36; 99,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,39; 99,84</t>
+          <t>92,69; 99,58</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,97; 98,03</t>
+          <t>58,52; 98,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,43; 98,32</t>
+          <t>60,7; 97,59</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,02; 97,62</t>
+          <t>89,13; 97,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,57; 98,12</t>
+          <t>90,58; 97,67</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43070</t>
+          <t>42998</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52756</t>
+          <t>53192</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37893; 44952</t>
+          <t>38636; 44920</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48596; 55002</t>
+          <t>49044; 55449</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>79975</t>
+          <t>87561</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105347</t>
+          <t>114888</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74948; 81600</t>
+          <t>81575; 89790</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100062; 106971</t>
+          <t>109008; 117105</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>26240</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13378; 23018</t>
+          <t>16051; 26980</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15342; 25383</t>
+          <t>18097; 29097</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>142904</t>
+          <t>154412</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180297</t>
+          <t>194320</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>133123; 147641</t>
+          <t>145911; 159528</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170850; 185090</t>
+          <t>184425; 198861</t>
         </is>
       </c>
     </row>
